--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-06.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-06.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T3"/>
+  <dimension ref="A1:T6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,15 +578,19 @@
       <c r="K2" t="n">
         <v>1.49</v>
       </c>
-      <c r="L2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>✅ LIQUIDADO</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -660,15 +664,19 @@
       <c r="K3" t="n">
         <v>2.2</v>
       </c>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>✅ LIQUIDADO</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -692,6 +700,264 @@
       </c>
       <c r="T3" t="n">
         <v>10.06</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Chinese League 1</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Changchun Yatai x Yanbian Longding</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Changchun Yatai</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Yanbian Longding</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lay 2x2 Top 3 (Aprovado)</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>19</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>✅ LIQUIDADO</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>161</v>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="R4" t="n">
+        <v>200</v>
+      </c>
+      <c r="S4" t="n">
+        <v>11.11</v>
+      </c>
+      <c r="T4" t="n">
+        <v>10.61</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Chinese League 1</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Wuxi Wugou x Suzhou Dongwu</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Wuxi Wugou</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Suzhou Dongwu</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lay 2x2 Top 3 (Aprovado)</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>✅ LIQUIDADO</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>271</v>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="R5" t="n">
+        <v>200</v>
+      </c>
+      <c r="S5" t="n">
+        <v>11.43</v>
+      </c>
+      <c r="T5" t="n">
+        <v>10.92</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Chinese League 2</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Guangdong Mingtu x Dalian Yingbo II</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Guangdong Mingtu</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Dalian Yingbo II</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lay Over 4.5 FT (Under Pesado)</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>19</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>✅ LIQUIDADO</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>1374</v>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="R6" t="n">
+        <v>200</v>
+      </c>
+      <c r="S6" t="n">
+        <v>11.11</v>
+      </c>
+      <c r="T6" t="n">
+        <v>10.61</v>
       </c>
     </row>
   </sheetData>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-06.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T6"/>
+  <dimension ref="A1:T7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -958,6 +958,88 @@
       </c>
       <c r="T6" t="n">
         <v>10.61</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Norwegian Cup</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Raufoss x Start</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Raufoss</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Start</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lay Home/DC X2 (FavVis &lt;= 1.65)</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>7</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>257</v>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="R7" t="n">
+        <v>200</v>
+      </c>
+      <c r="S7" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="T7" t="n">
+        <v>31.83</v>
       </c>
     </row>
   </sheetData>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-06.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T7"/>
+  <dimension ref="A1:T4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,32 +538,32 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Chinese League 2</t>
+          <t>Chinese League 1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Shanghai Second x Wenzhou Professional</t>
+          <t>Changchun Yatai x Yanbian Longding</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Shanghai Second</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Wenzhou Professional</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lay Over 4.5 FT (Under Pesado)</t>
+          <t>Lay 2x2 Top 3 (Aprovado)</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
@@ -576,7 +576,7 @@
         <v>19</v>
       </c>
       <c r="K2" t="n">
-        <v>1.49</v>
+        <v>1.99</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -599,11 +599,11 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>419</v>
+        <v>161</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="R2" t="n">
@@ -624,27 +624,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Chinese League 2</t>
+          <t>Chinese League 1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Hubei Istar x Lanzhou Longyuan Athletic</t>
+          <t>Wuxi Wugou x Suzhou Dongwu</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Hubei Istar</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lanzhou Longyuan Athletic</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -659,19 +659,19 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="K3" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>2-2</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>RED</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -685,21 +685,21 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>68</v>
+        <v>271</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="R3" t="n">
         <v>200</v>
       </c>
       <c r="S3" t="n">
-        <v>10.53</v>
+        <v>11.43</v>
       </c>
       <c r="T3" t="n">
-        <v>10.06</v>
+        <v>10.92</v>
       </c>
     </row>
     <row r="4">
@@ -710,32 +710,32 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Chinese League 1</t>
+          <t>Norwegian Cup</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Changchun Yatai x Yanbian Longding</t>
+          <t>Raufoss x Start</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lay 2x2 Top 3 (Aprovado)</t>
+          <t>Lay Home/DC X2 (FavVis &lt;= 1.65)</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
@@ -745,14 +745,14 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="K4" t="n">
-        <v>1.99</v>
+        <v>1.5</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>AO Away Win</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -771,274 +771,20 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>161</v>
+        <v>257</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="R4" t="n">
         <v>200</v>
       </c>
       <c r="S4" t="n">
-        <v>11.11</v>
+        <v>33.33</v>
       </c>
       <c r="T4" t="n">
-        <v>10.61</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Chinese League 1</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Wuxi Wugou x Suzhou Dongwu</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Wuxi Wugou</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Suzhou Dongwu</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Lay 2x2 Top 3 (Aprovado)</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>LAY</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="K5" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>2-2</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>RED</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>✅ LIQUIDADO</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>coletor (KO-10)</t>
-        </is>
-      </c>
-      <c r="P5" t="n">
-        <v>271</v>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="R5" t="n">
-        <v>200</v>
-      </c>
-      <c r="S5" t="n">
-        <v>11.43</v>
-      </c>
-      <c r="T5" t="n">
-        <v>10.92</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Chinese League 2</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Guangdong Mingtu x Dalian Yingbo II</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Guangdong Mingtu</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Dalian Yingbo II</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Lay Over 4.5 FT (Under Pesado)</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>LAY</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v>19</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>1-1</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>GREEN</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>✅ LIQUIDADO</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>coletor (KO-10)</t>
-        </is>
-      </c>
-      <c r="P6" t="n">
-        <v>1374</v>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="R6" t="n">
-        <v>200</v>
-      </c>
-      <c r="S6" t="n">
-        <v>11.11</v>
-      </c>
-      <c r="T6" t="n">
-        <v>10.61</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Norwegian Cup</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Raufoss x Start</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Raufoss</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Start</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Lay Home/DC X2 (FavVis &lt;= 1.65)</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>LAY</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
-        <v>7</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>PENDENTE</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>⏳ PENDENTE</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>coletor (KO-10)</t>
-        </is>
-      </c>
-      <c r="P7" t="n">
-        <v>257</v>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="R7" t="n">
-        <v>200</v>
-      </c>
-      <c r="S7" t="n">
-        <v>33.33</v>
-      </c>
-      <c r="T7" t="n">
         <v>31.83</v>
       </c>
     </row>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-06.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T4"/>
+  <dimension ref="A1:P5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,26 +509,6 @@
           <t>Liquidez_Lay</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>Hora_Str</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>Risco_Red_R$</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Stake_Sugerida_R$</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>Lucro_Green_R$</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -601,20 +581,6 @@
       <c r="P2" t="n">
         <v>161</v>
       </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="R2" t="n">
-        <v>200</v>
-      </c>
-      <c r="S2" t="n">
-        <v>11.11</v>
-      </c>
-      <c r="T2" t="n">
-        <v>10.61</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -687,20 +653,6 @@
       <c r="P3" t="n">
         <v>271</v>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="R3" t="n">
-        <v>200</v>
-      </c>
-      <c r="S3" t="n">
-        <v>11.43</v>
-      </c>
-      <c r="T3" t="n">
-        <v>10.92</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -773,19 +725,73 @@
       <c r="P4" t="n">
         <v>257</v>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="R4" t="n">
-        <v>200</v>
-      </c>
-      <c r="S4" t="n">
-        <v>33.33</v>
-      </c>
-      <c r="T4" t="n">
-        <v>31.83</v>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>21:35</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Brazilian Serie B</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Ponte Preta x Juventude</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Ponte Preta</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Juventude</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>707</v>
       </c>
     </row>
   </sheetData>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-06.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P5"/>
+  <dimension ref="A1:P3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -518,32 +518,32 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Chinese League 1</t>
+          <t>Norwegian Cup</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Changchun Yatai x Yanbian Longding</t>
+          <t>Raufoss x Start</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lay 2x2 Top 3 (Aprovado)</t>
+          <t>Lay Home/DC X2 (FavVis &lt;= 1.65)</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
@@ -553,14 +553,14 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="K2" t="n">
-        <v>1.99</v>
+        <v>1.5</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>AO Away Win</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -579,7 +579,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>161</v>
+        <v>257</v>
       </c>
     </row>
     <row r="3">
@@ -590,32 +590,32 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>21:35</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Chinese League 1</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Wuxi Wugou x Suzhou Dongwu</t>
+          <t>Ponte Preta x Juventude</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lay 2x2 Top 3 (Aprovado)</t>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
@@ -625,24 +625,20 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>18.5</v>
+        <v>6.2</v>
       </c>
       <c r="K3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>2-2</t>
-        </is>
-      </c>
+        <v>1.29</v>
+      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>RED</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>✅ LIQUIDADO</t>
+          <t>⏳ PENDENTE</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -651,146 +647,6 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Norwegian Cup</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Raufoss x Start</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Raufoss</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Start</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Lay Home/DC X2 (FavVis &lt;= 1.65)</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>LAY</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
-        <v>7</v>
-      </c>
-      <c r="K4" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>AO Away Win</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>GREEN</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>✅ LIQUIDADO</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>coletor (KO-10)</t>
-        </is>
-      </c>
-      <c r="P4" t="n">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>21:35</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Brazilian Serie B</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Ponte Preta x Juventude</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Ponte Preta</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Juventude</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Lay Draw (Fav &lt;= 1.40)</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>LAY</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>PENDENTE</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>⏳ PENDENTE</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>coletor (KO-10)</t>
-        </is>
-      </c>
-      <c r="P5" t="n">
         <v>707</v>
       </c>
     </row>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-06.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-06.xlsx
@@ -630,15 +630,19 @@
       <c r="K3" t="n">
         <v>1.29</v>
       </c>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>✅ LIQUIDADO</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-06.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-06.xlsx
@@ -558,19 +558,15 @@
       <c r="K2" t="n">
         <v>1.5</v>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>AO Away Win</t>
-        </is>
-      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>✅ LIQUIDADO</t>
+          <t>⏳ PENDENTE</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -630,19 +626,15 @@
       <c r="K3" t="n">
         <v>1.29</v>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>0-2</t>
-        </is>
-      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>✅ LIQUIDADO</t>
+          <t>⏳ PENDENTE</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-06.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-06.xlsx
@@ -558,15 +558,19 @@
       <c r="K2" t="n">
         <v>1.5</v>
       </c>
-      <c r="L2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>2x0</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>RED</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>🔴 RED</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -626,15 +630,19 @@
       <c r="K3" t="n">
         <v>1.29</v>
       </c>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>0x0</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>RED</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>🔴 RED</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
